--- a/Data Visualization/Dear Data/Dear Data.xlsx
+++ b/Data Visualization/Dear Data/Dear Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\GitHub\Zoes-Hagenberg-3-The-Hagening\Data Visualization\Dear Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA354AF4-AC98-4BF7-B57E-56EA361C4410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF6938-EDDA-422A-9545-EBD316DFF46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>The Slow Dance</t>
-  </si>
-  <si>
-    <t>Falling in Love With a Corporate Illusion</t>
   </si>
   <si>
     <t>Webpunk</t>
@@ -470,6 +467,9 @@
   </si>
   <si>
     <t>I think it's an interesting insight in how emotions and feelings affect music listening habits.</t>
+  </si>
+  <si>
+    <t>Falling in Love With a Corporate Illustration</t>
   </si>
 </sst>
 </file>
@@ -11328,7 +11328,7 @@
     </row>
     <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -11361,7 +11361,7 @@
     </row>
     <row r="3" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -11394,7 +11394,7 @@
     </row>
     <row r="4" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -11427,7 +11427,7 @@
     </row>
     <row r="5" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="6" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="7" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -11526,7 +11526,7 @@
     </row>
     <row r="8" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -11547,7 +11547,7 @@
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U8" s="9"/>
       <c r="V8" s="9"/>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="9" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="10" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="12" spans="1:29" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -11776,7 +11776,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="9"/>
       <c r="J15" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
@@ -11821,7 +11821,7 @@
       <c r="H16" s="5"/>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
@@ -11864,7 +11864,7 @@
       <c r="H17" s="5"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -11952,7 +11952,7 @@
       <c r="H19" s="5"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -11997,7 +11997,7 @@
       <c r="H20" s="5"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -12040,7 +12040,7 @@
       <c r="H21" s="5"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -12083,7 +12083,7 @@
       <c r="H22" s="5"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -12130,7 +12130,7 @@
       <c r="H23" s="5"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -12176,7 +12176,7 @@
       <c r="H24" s="5"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
@@ -12220,7 +12220,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -12310,7 +12310,7 @@
       <c r="H27" s="5"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -12356,7 +12356,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -12400,7 +12400,7 @@
       <c r="H29" s="5"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -12444,7 +12444,7 @@
       <c r="H30" s="5"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -12492,7 +12492,7 @@
       <c r="H31" s="5"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -12538,7 +12538,7 @@
       <c r="H32" s="5"/>
       <c r="I32" s="9"/>
       <c r="J32" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
@@ -12569,7 +12569,7 @@
         <v>1342</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="E33" s="16">
         <v>19</v>
@@ -12581,7 +12581,7 @@
       <c r="H33" s="5"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
@@ -12612,7 +12612,7 @@
         <v>1100</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="16">
         <v>19</v>
@@ -12624,7 +12624,7 @@
       <c r="H34" s="5"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -12700,7 +12700,7 @@
         <v>816</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="16">
         <v>30</v>
@@ -12714,7 +12714,7 @@
       <c r="H36" s="5"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
@@ -12745,19 +12745,19 @@
         <v>309</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" s="16">
         <v>26</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="18"/>
       <c r="H37" s="5"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
@@ -12782,7 +12782,7 @@
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="15">
         <v>300</v>
@@ -12845,7 +12845,7 @@
       <c r="H39" s="5"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
@@ -12876,7 +12876,7 @@
         <v>1296</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40" s="16">
         <v>28</v>
@@ -12890,7 +12890,7 @@
       <c r="H40" s="5"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
@@ -12921,7 +12921,7 @@
         <v>858</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="16">
         <v>28</v>
@@ -12933,7 +12933,7 @@
       <c r="H41" s="5"/>
       <c r="I41" s="9"/>
       <c r="J41" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
@@ -12964,7 +12964,7 @@
         <v>417</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E42" s="16">
         <v>27</v>
@@ -12976,7 +12976,7 @@
       <c r="H42" s="5"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
@@ -13023,7 +13023,7 @@
       <c r="H43" s="5"/>
       <c r="I43" s="9"/>
       <c r="J43" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
@@ -13054,13 +13054,13 @@
         <v>816</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" s="16">
         <v>30</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G44" s="17">
         <v>4669</v>
@@ -13068,7 +13068,7 @@
       <c r="H44" s="5"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
@@ -13093,13 +13093,13 @@
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="15">
         <v>378</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" s="16">
         <v>25</v>
@@ -13111,7 +13111,7 @@
       <c r="H45" s="5"/>
       <c r="I45" s="9"/>
       <c r="J45" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -13142,13 +13142,13 @@
         <v>316</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="16">
         <v>22</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="5"/>
@@ -13199,7 +13199,7 @@
       <c r="H47" s="5"/>
       <c r="I47" s="9"/>
       <c r="J47" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
@@ -13224,19 +13224,19 @@
     <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="15">
         <v>528</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E48" s="16">
         <v>23</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="17">
         <v>6812</v>
@@ -13244,7 +13244,7 @@
       <c r="H48" s="5"/>
       <c r="I48" s="9"/>
       <c r="J48" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
@@ -13269,25 +13269,25 @@
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="15">
         <v>462</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E49" s="16">
         <v>21</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G49" s="18"/>
       <c r="H49" s="5"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
@@ -13318,13 +13318,13 @@
         <v>360</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E50" s="16">
         <v>21</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="5"/>
@@ -13375,7 +13375,7 @@
       <c r="H51" s="5"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
@@ -13406,13 +13406,13 @@
         <v>1224</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" s="16">
         <v>38</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G52" s="17">
         <v>8196</v>
@@ -13420,7 +13420,7 @@
       <c r="H52" s="5"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
@@ -13445,25 +13445,25 @@
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="15">
         <v>876</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" s="16">
         <v>33</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G53" s="18"/>
       <c r="H53" s="5"/>
       <c r="I53" s="9"/>
       <c r="J53" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
@@ -13494,19 +13494,19 @@
         <v>612</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E54" s="16">
         <v>32</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" s="20"/>
       <c r="H54" s="5"/>
       <c r="I54" s="9"/>
       <c r="J54" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
@@ -13582,13 +13582,13 @@
         <v>2597</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E56" s="16">
         <v>44</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G56" s="17">
         <v>9641</v>
@@ -13596,7 +13596,7 @@
       <c r="H56" s="5"/>
       <c r="I56" s="9"/>
       <c r="J56" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
@@ -13621,25 +13621,25 @@
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="15">
         <v>1494</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E57" s="16">
         <v>36</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G57" s="18"/>
       <c r="H57" s="5"/>
       <c r="I57" s="9"/>
       <c r="J57" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
@@ -13670,19 +13670,19 @@
         <v>300</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E58" s="16">
         <v>33</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G58" s="20"/>
       <c r="H58" s="5"/>
       <c r="I58" s="9"/>
       <c r="J58" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
@@ -13729,7 +13729,7 @@
       <c r="H59" s="5"/>
       <c r="I59" s="9"/>
       <c r="J59" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
@@ -13760,7 +13760,7 @@
         <v>2572</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" s="16">
         <v>33</v>
@@ -13774,7 +13774,7 @@
       <c r="H60" s="5"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
@@ -13805,7 +13805,7 @@
         <v>422</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" s="16">
         <v>33</v>
@@ -13846,7 +13846,7 @@
         <v>211</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" s="16">
         <v>30</v>
@@ -13858,7 +13858,7 @@
       <c r="H62" s="5"/>
       <c r="I62" s="9"/>
       <c r="J62" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K62" s="9"/>
       <c r="L62" s="9"/>
@@ -13905,7 +13905,7 @@
       <c r="H63" s="5"/>
       <c r="I63" s="9"/>
       <c r="J63" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
@@ -13936,13 +13936,13 @@
         <v>1103</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E64" s="16">
         <v>32</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G64" s="17">
         <v>7692</v>
@@ -13950,7 +13950,7 @@
       <c r="H64" s="5"/>
       <c r="I64" s="9"/>
       <c r="J64" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K64" s="9"/>
       <c r="L64" s="9"/>
@@ -13981,13 +13981,13 @@
         <v>200</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E65" s="16">
         <v>28</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G65" s="18"/>
       <c r="H65" s="5"/>
@@ -14022,19 +14022,19 @@
         <v>172</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E66" s="16">
         <v>20</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G66" s="20"/>
       <c r="H66" s="5"/>
       <c r="I66" s="9"/>
       <c r="J66" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K66" s="9"/>
       <c r="L66" s="9"/>
@@ -14067,7 +14067,7 @@
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="J67" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
@@ -14078,7 +14078,7 @@
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
       <c r="S67" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T67" s="9"/>
       <c r="U67" s="9"/>
@@ -14102,7 +14102,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
       <c r="J68" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K68" s="9"/>
       <c r="L68" s="9"/>
@@ -14127,7 +14127,7 @@
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="9"/>
       <c r="B69" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -14160,7 +14160,7 @@
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
@@ -14170,7 +14170,7 @@
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
       <c r="J70" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K70" s="9"/>
       <c r="L70" s="9"/>
@@ -14203,7 +14203,7 @@
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
       <c r="J71" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K71" s="9"/>
       <c r="L71" s="9"/>
@@ -14267,7 +14267,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
       <c r="J73" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
@@ -14300,7 +14300,7 @@
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
       <c r="J74" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
@@ -14333,7 +14333,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
       <c r="J75" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
@@ -16026,15 +16026,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
         <v>69</v>
-      </c>
-      <c r="B1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1">
         <v>3044</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1">
         <v>5601</v>
@@ -16050,7 +16050,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="1">
         <v>9887</v>
@@ -16058,7 +16058,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="1">
         <v>9062</v>
@@ -16066,7 +16066,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1">
         <v>9151</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="1">
         <v>3268</v>
@@ -16082,7 +16082,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1">
         <v>4025</v>
@@ -16090,7 +16090,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1">
         <v>4669</v>
@@ -16098,7 +16098,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1">
         <v>6812</v>
@@ -16106,7 +16106,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="1">
         <v>8196</v>
@@ -16114,7 +16114,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="1">
         <v>9641</v>
@@ -16122,7 +16122,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1">
         <v>6306</v>
@@ -16130,7 +16130,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="1">
         <v>7692</v>
@@ -16138,13 +16138,13 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -16196,7 +16196,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32" s="1">
         <v>2370</v>
@@ -16251,7 +16251,7 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37">
         <v>762</v>
@@ -16262,7 +16262,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38">
         <v>528</v>
@@ -16295,7 +16295,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41">
         <v>378</v>
